--- a/data/trans_dic/P39A3_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P39A3_2023-Estudios-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que sí diría que estar con dolor o malestar en el pecho es un síntoma de que a alguien le está dando un ataque al corazón</t>
+          <t>Población que sí diría que estar con dolor o malestar en el pecho es un síntoma de que a alguien le está dando un ataque al corazón (tasa de respuesta: 93,03%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>89,19; 94,15</t>
+          <t>89,21; 93,92</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>90,47; 93,82</t>
+          <t>90,44; 93,84</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>90,58; 93,4</t>
+          <t>90,59; 93,26</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>90,64; 94,61</t>
+          <t>90,53; 94,73</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>78,64; 92,47</t>
+          <t>78,07; 92,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>85,46; 92,55</t>
+          <t>85,41; 92,73</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>88,73; 92,98</t>
+          <t>88,82; 93,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>86,72; 90,67</t>
+          <t>86,84; 90,8</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>88,32; 91,39</t>
+          <t>88,39; 91,35</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>90,8; 93,74</t>
+          <t>90,83; 93,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>82,51; 91,77</t>
+          <t>82,49; 91,71</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>86,92; 92,12</t>
+          <t>86,99; 92,03</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que sí diría que estar con dolor o malestar en el pecho es un síntoma de que a alguien le está dando un ataque al corazón</t>
+          <t>Población que sí diría que estar con dolor o malestar en el pecho es un síntoma de que a alguien le está dando un ataque al corazón (tasa de respuesta: 93,03%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>393616; 415519</t>
+          <t>393725; 414508</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>573929; 595211</t>
+          <t>573742; 595321</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>974385; 1004749</t>
+          <t>974504; 1003254</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1976947; 2063696</t>
+          <t>1974661; 2066243</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1667608; 1960834</t>
+          <t>1655438; 1961673</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3676309; 3981400</t>
+          <t>3674015; 3989140</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>559479; 586242</t>
+          <t>560049; 586947</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>561926; 587574</t>
+          <t>562725; 588409</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1129242; 1168414</t>
+          <t>1130090; 1167914</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2953920; 3049575</t>
+          <t>2954623; 3056430</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2807868; 3122854</t>
+          <t>2807210; 3120856</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5785078; 6131743</t>
+          <t>5790244; 6125667</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P39A3_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P39A3_2023-Estudios-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>92,02%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>91,76%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>89,21; 93,92</t>
+          <t>88,67; 93,52</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>90,44; 93,84</t>
+          <t>90,17; 93,42</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>90,59; 93,26</t>
+          <t>90,25; 93,09</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>90,54%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>90,73%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>90,53; 94,73</t>
+          <t>89,36; 92,33</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>78,07; 92,51</t>
+          <t>89,36; 91,53</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>85,41; 92,73</t>
+          <t>89,8; 91,59</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>88,82%</t>
+          <t>88,38%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>89,44%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>88,82; 93,09</t>
+          <t>88,16; 92,35</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>86,84; 90,8</t>
+          <t>86,1; 90,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>88,39; 91,35</t>
+          <t>87,84; 90,84</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>90,89%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>90,39%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>90,7%</t>
+          <t>90,63%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>90,83; 93,96</t>
+          <t>89,79; 91,87</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>82,49; 91,71</t>
+          <t>89,5; 91,18</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>86,99; 92,03</t>
+          <t>89,87; 91,29</t>
         </is>
       </c>
     </row>
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>405300</t>
+          <t>441222</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>585001</t>
+          <t>632768</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>990300</t>
+          <t>1073990</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>393725; 414508</t>
+          <t>428157; 451547</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>573742; 595321</t>
+          <t>620031; 642349</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>974504; 1003254</t>
+          <t>1056358; 1089516</t>
         </is>
       </c>
     </row>
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2013853</t>
+          <t>1900823</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1882394</t>
+          <t>1867220</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3896247</t>
+          <t>3768044</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1974661; 2066243</t>
+          <t>1868476; 1930674</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1655438; 1961673</t>
+          <t>1842753; 1887548</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3674015; 3989140</t>
+          <t>3729534; 3803753</t>
         </is>
       </c>
     </row>
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>574956</t>
+          <t>627934</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>575577</t>
+          <t>634958</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1150533</t>
+          <t>1262892</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>560049; 586947</t>
+          <t>611510; 640597</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>562725; 588409</t>
+          <t>618575; 647440</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1130090; 1167914</t>
+          <t>1240322; 1282655</t>
         </is>
       </c>
     </row>
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2994107</t>
+          <t>2969980</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3042973</t>
+          <t>3134945</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6037080</t>
+          <t>6104926</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2954623; 3056430</t>
+          <t>2934026; 3001823</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2807210; 3120856</t>
+          <t>3104192; 3162370</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5790244; 6125667</t>
+          <t>6053114; 6149068</t>
         </is>
       </c>
     </row>
